--- a/per-stock/DLR/financials.xlsx
+++ b/per-stock/DLR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67429851136</v>
+        <v>67301076992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85991391232</v>
+        <v>85864890368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.00265</v>
+        <v>50.03989</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60.59057</v>
+        <v>65.69162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.6793375</v>
+        <v>10.658943</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3261901824</v>
+        <v>3278001664</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>yfinance info.freeCashflow (FALLBACK levered estimate — statement TTM unavailable)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>188.51</v>
+        <v>188.15</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -790,7 +799,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D56</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C56</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B56</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B53:E53)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B51:E51)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D4/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C4/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1136,265 +1604,265 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total Operating Income As Reported</t>
+          <t>Rent Expense Supplemental</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>658492000</v>
+        <v>2726737000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>471864000</v>
+        <v>2519115000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>524461000</v>
+        <v>2598071000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>589968000</v>
+        <v>2017562000</v>
       </c>
       <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Diluted Average Shares</t>
+          <t>Total Operating Income As Reported</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>347810000</v>
+        <v>658492000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>331547000</v>
+        <v>471864000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>309065000</v>
+        <v>524461000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>297919336</v>
+        <v>589968000</v>
       </c>
       <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Basic Average Shares</t>
+          <t>Diluted Average Shares</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>339807000</v>
+        <v>347810000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>323336000</v>
+        <v>331547000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>298603000</v>
+        <v>309065000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>286333747</v>
+        <v>297919336</v>
       </c>
       <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diluted EPS</t>
+          <t>Basic Average Shares</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.58</v>
+        <v>339807000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.61</v>
+        <v>323336000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>298603000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.13</v>
+        <v>286333747</v>
       </c>
       <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Basic EPS</t>
+          <t>Diluted EPS</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Diluted NI Availto Com Stockholders</t>
+          <t>Basic EPS</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1245272000</v>
+        <v>3.73</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>534707000</v>
+        <v>1.74</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>890021000</v>
+        <v>3.04</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>332121000</v>
+        <v>1.18</v>
       </c>
       <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Average Dilution Earnings</t>
+          <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-22593000</v>
+        <v>1245272000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-27059000</v>
+        <v>534707000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-18093000</v>
+        <v>890021000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-4839000</v>
+        <v>332121000</v>
       </c>
       <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Income Common Stockholders</t>
+          <t>Average Dilution Earnings</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1267865000</v>
+        <v>-22593000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>561766000</v>
+        <v>-27059000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>908114000</v>
+        <v>-18093000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>336960000</v>
+        <v>-4839000</v>
       </c>
       <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Otherunder Preferred Stock Dividend</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1267865000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>561766000</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>908114000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-18000000</v>
-      </c>
+        <v>336960000</v>
+      </c>
+      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Preferred Stock Dividends</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>40724000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>40724000</v>
-      </c>
+          <t>Otherunder Preferred Stock Dividend</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>40724000</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>40724000</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-18000000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Preferred Stock Dividends</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1308589000</v>
+        <v>40724000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>602490000</v>
+        <v>40724000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>948838000</v>
+        <v>40724000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>377684000</v>
+        <v>40724000</v>
       </c>
       <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Minority Interests</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-4576000</v>
+        <v>1308589000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>14163000</v>
+        <v>602490000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-1474000</v>
+        <v>948838000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-2641000</v>
+        <v>377684000</v>
       </c>
       <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Minority Interests</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1313165000</v>
+        <v>-4576000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>588327000</v>
+        <v>14163000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>950312000</v>
+        <v>-1474000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>380325000</v>
+        <v>-2641000</v>
       </c>
       <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
+          <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1414,357 +1882,357 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>32040000</v>
+        <v>1313165000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>54760000</v>
+        <v>588327000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>75579000</v>
+        <v>950312000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>31550000</v>
+        <v>380325000</v>
       </c>
       <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1345205000</v>
+        <v>32040000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>643087000</v>
+        <v>54760000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1025891000</v>
+        <v>75579000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>411875000</v>
+        <v>31550000</v>
       </c>
       <c r="F32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>861017000</v>
+        <v>1345205000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>338973000</v>
+        <v>643087000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>736086000</v>
+        <v>1025891000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>49273000</v>
+        <v>411875000</v>
       </c>
       <c r="F33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
+          <t>Other Income Expense</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>161052000</v>
+        <v>861017000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>154243000</v>
+        <v>338973000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>68431000</v>
+        <v>736086000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>8917000</v>
+        <v>49273000</v>
       </c>
       <c r="F34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Special Income Charges</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-263634000</v>
+        <v>161052000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-290957000</v>
+        <v>154243000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-203085000</v>
+        <v>68431000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-122901000</v>
+        <v>8917000</v>
       </c>
       <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Business</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Special Income Charges</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-263634000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-290957000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-203085000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-122901000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Other Special Charges</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>5871000</v>
-      </c>
+          <t>Gain On Sale Of Business</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n">
-        <v>51135000</v>
-      </c>
+      <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n">
-        <v>18672000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Write Off</t>
+          <t>Other Special Charges</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>78553000</v>
+        <v>-9000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>191184000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>118363000</v>
-      </c>
+        <v>5871000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F38" s="3" t="n"/>
+        <v>51135000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>18672000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Impairment Of Capital Assets</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+          <t>Write Off</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>78553000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>191184000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>118363000</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>18291000</v>
-      </c>
+      <c r="F39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Restructuring And Mergern Acquisition</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>185090000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>93902000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>84722000</v>
-      </c>
+          <t>Impairment Of Capital Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n">
-        <v>68766000</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
+        <v>3000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>18291000</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Earnings From Equity Interest</t>
+          <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-31987000</v>
+        <v>185090000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-120138000</v>
+        <v>93902000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-29791000</v>
+        <v>84722000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-13497000</v>
+        <v>68766000</v>
       </c>
       <c r="F41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
+          <t>Earnings From Equity Interest</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>995586000</v>
+        <v>-31987000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>595825000</v>
+        <v>-120138000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>900531000</v>
+        <v>-29791000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>176754000</v>
+        <v>-13497000</v>
       </c>
       <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-437947000</v>
+        <v>995586000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-452836000</v>
+        <v>595825000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-437741000</v>
+        <v>900531000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-299132000</v>
+        <v>176754000</v>
       </c>
       <c r="F43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Interest Expense Non Operating</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>437947000</v>
+        <v>-437947000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>452836000</v>
+        <v>-452836000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>437741000</v>
+        <v>-437741000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>299132000</v>
+        <v>-299132000</v>
       </c>
       <c r="F44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>922135000</v>
+        <v>437947000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>756950000</v>
+        <v>452836000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>727546000</v>
+        <v>437741000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>661734000</v>
+        <v>299132000</v>
       </c>
       <c r="F45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2463820000</v>
+        <v>922135000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2278903000</v>
+        <v>756950000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2151444000</v>
+        <v>727546000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2012538000</v>
+        <v>661734000</v>
       </c>
       <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other Operating Expenses</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>3702000</v>
+        <v>2463820000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>27083000</v>
+        <v>2278903000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>7529000</v>
+        <v>2151444000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>12438000</v>
+        <v>2012538000</v>
       </c>
       <c r="F47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1894636000</v>
+        <v>3702000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1771797000</v>
+        <v>27083000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1694859000</v>
+        <v>7529000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1577933000</v>
+        <v>12438000</v>
       </c>
       <c r="F48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization In Income Statement</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -1784,27 +2252,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>565482000</v>
+        <v>1894636000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>480023000</v>
+        <v>1771797000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>449056000</v>
+        <v>1694859000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>422167000</v>
+        <v>1577933000</v>
       </c>
       <c r="F50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -1824,7 +2292,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>General And Administrative Expense</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -1844,67 +2312,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Other Gand A</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>3385955000</v>
+        <v>565482000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>3035853000</v>
+        <v>480023000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2878990000</v>
+        <v>449056000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2674272000</v>
+        <v>422167000</v>
       </c>
       <c r="F53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2726737000</v>
+        <v>3385955000</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2519115000</v>
+        <v>3035853000</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2598071000</v>
+        <v>2878990000</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2017562000</v>
+        <v>2674272000</v>
       </c>
       <c r="F54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>6112692000</v>
+        <v>2726737000</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>5554968000</v>
+        <v>2519115000</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>5477061000</v>
+        <v>2598071000</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>4691834000</v>
+        <v>2017562000</v>
       </c>
       <c r="F55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -1920,19 +2388,39 @@
         <v>4691834000</v>
       </c>
       <c r="F56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>6112692000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5554968000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5477061000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>4691834000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2350,23 +2838,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total Operating Income As Reported</t>
+          <t>Rent Expense Supplemental</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>266933000</v>
+        <v>698263000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>112624000</v>
+        <v>749635000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>138421000</v>
+        <v>710250000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>211697000</v>
+        <v>661528000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>195750000</v>
+        <v>605324000</v>
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
@@ -2374,23 +2862,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Diluted Average Shares</t>
+          <t>Total Operating Income As Reported</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>353254000</v>
+        <v>266933000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>351570000</v>
+        <v>112624000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>349234000</v>
+        <v>138421000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>345734000</v>
+        <v>211697000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>344721000</v>
+        <v>195750000</v>
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="n"/>
@@ -2398,23 +2886,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Basic Average Shares</t>
+          <t>Diluted Average Shares</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>345013000</v>
+        <v>353255000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>343493000</v>
+        <v>351570000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>341370000</v>
+        <v>349234000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>337589000</v>
+        <v>345734000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>336683000</v>
+        <v>344721000</v>
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
@@ -2422,23 +2910,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diluted EPS</t>
+          <t>Basic Average Shares</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.46</v>
+        <v>345013000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.24</v>
+        <v>343493000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.15</v>
+        <v>341370000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.94</v>
+        <v>337589000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.27</v>
+        <v>336683000</v>
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
@@ -2446,23 +2934,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Basic EPS</t>
+          <t>Diluted EPS</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
@@ -2470,23 +2958,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Diluted NI Availto Com Stockholders</t>
+          <t>Basic EPS</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>160777000</v>
+        <v>0.49</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>83953000</v>
+        <v>0.26</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>51761000</v>
+        <v>0.17</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1015960000</v>
+        <v>3.03</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>93598000</v>
+        <v>0.3</v>
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
@@ -2494,23 +2982,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Average Dilution Earnings</t>
+          <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-8316000</v>
+        <v>160777000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-4513000</v>
+        <v>83953000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-5870000</v>
+        <v>51761000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-6015000</v>
+        <v>1015960000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-6195000</v>
+        <v>93598000</v>
       </c>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
@@ -2518,23 +3006,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Income Common Stockholders</t>
+          <t>Average Dilution Earnings</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>169093000</v>
+        <v>-8316000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>88466000</v>
+        <v>-4513000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>57631000</v>
+        <v>-5870000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1021975000</v>
+        <v>-6015000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>99793000</v>
+        <v>-6195000</v>
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
@@ -2542,23 +3030,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Preferred Stock Dividends</t>
+          <t>Net Income Common Stockholders</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10181000</v>
+        <v>169093000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>10181000</v>
+        <v>88466000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>10181000</v>
+        <v>57631000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10181000</v>
+        <v>1021975000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10181000</v>
+        <v>99793000</v>
       </c>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
@@ -2566,23 +3054,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Preferred Stock Dividends</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>179274000</v>
+        <v>10181000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>98647000</v>
+        <v>10181000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67812000</v>
+        <v>10181000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1032156000</v>
+        <v>10181000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>109974000</v>
+        <v>10181000</v>
       </c>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
@@ -2590,23 +3078,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Minority Interests</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4470000</v>
+        <v>179274000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2536000</v>
+        <v>98647000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4099000</v>
+        <v>67812000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14790000</v>
+        <v>1032156000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3579000</v>
+        <v>109974000</v>
       </c>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
@@ -2614,23 +3102,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Minority Interests</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>174804000</v>
+        <v>4470000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>96111000</v>
+        <v>2536000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>63713000</v>
+        <v>4099000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1046946000</v>
+        <v>-14790000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>106395000</v>
+        <v>3579000</v>
       </c>
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
@@ -2638,7 +3126,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
+          <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -2662,23 +3150,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>16008000</v>
+        <v>174804000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-9673000</v>
+        <v>96111000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>11695000</v>
+        <v>63713000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>12883000</v>
+        <v>1046946000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>17135000</v>
+        <v>106395000</v>
       </c>
       <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="n"/>
@@ -2686,23 +3174,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>190812000</v>
+        <v>16008000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>86438000</v>
+        <v>-9673000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>75408000</v>
+        <v>11695000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1059829000</v>
+        <v>12883000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>123530000</v>
+        <v>17135000</v>
       </c>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="n"/>
@@ -2710,23 +3198,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>24578000</v>
+        <v>190812000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-24306000</v>
+        <v>86438000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-35988000</v>
+        <v>75408000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>934969000</v>
+        <v>1059829000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-13658000</v>
+        <v>123530000</v>
       </c>
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n"/>
@@ -2734,23 +3222,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
+          <t>Other Income Expense</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>45342000</v>
+        <v>24578000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>42797000</v>
+        <v>-24306000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>47735000</v>
+        <v>-35988000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>37747000</v>
+        <v>934969000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>32773000</v>
+        <v>-13658000</v>
       </c>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
@@ -2758,23 +3246,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Special Income Charges</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-19804000</v>
+        <v>45342000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-114627000</v>
+        <v>42797000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-86559000</v>
+        <v>47735000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-22546000</v>
+        <v>37747000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-39902000</v>
+        <v>32773000</v>
       </c>
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="3" t="n"/>
@@ -2782,91 +3270,91 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Other Special Charges</t>
+          <t>Special Income Charges</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4119000</v>
-      </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n">
-        <v>2165000</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>2636000</v>
-      </c>
+        <v>-19804000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-114627000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-86559000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-22546000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>-39902000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Write Off</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n">
-        <v>78553000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4119000</v>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n">
-        <v>22881000</v>
+        <v>2165000</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2636000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Restructuring And Mergern Acquisition</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>15685000</v>
-      </c>
+          <t>Write Off</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
       <c r="C37" s="3" t="n">
-        <v>36083000</v>
+        <v>78553000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>86559000</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>22546000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>39902000</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>22881000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Earnings From Equity Interest</t>
+          <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-1833000</v>
+        <v>15685000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>4659000</v>
+        <v>36083000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-16944000</v>
+        <v>86559000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-12062000</v>
+        <v>22546000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>-7640000</v>
+        <v>39902000</v>
       </c>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n"/>
@@ -2874,23 +3362,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
+          <t>Earnings From Equity Interest</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>873000</v>
+        <v>-1833000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>42865000</v>
+        <v>4659000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>19780000</v>
+        <v>-16944000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>931830000</v>
+        <v>-12062000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1111000</v>
+        <v>-7640000</v>
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="n"/>
@@ -2898,23 +3386,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-116384000</v>
+        <v>873000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-116516000</v>
+        <v>42865000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-113584000</v>
+        <v>19780000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-109383000</v>
+        <v>931830000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-98464000</v>
+        <v>1111000</v>
       </c>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="n"/>
@@ -2922,23 +3410,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Interest Expense Non Operating</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>116384000</v>
+        <v>-116384000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>116516000</v>
+        <v>-116516000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>113584000</v>
+        <v>-113584000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>109383000</v>
+        <v>-109383000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>98464000</v>
+        <v>-98464000</v>
       </c>
       <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="n"/>
@@ -2946,23 +3434,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>282618000</v>
+        <v>116384000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>227260000</v>
+        <v>116516000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>224980000</v>
+        <v>113584000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>234243000</v>
+        <v>109383000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>235652000</v>
+        <v>98464000</v>
       </c>
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="n"/>
@@ -2970,23 +3458,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>654292000</v>
+        <v>282618000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>657776000</v>
+        <v>227260000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>642004000</v>
+        <v>224980000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>597379000</v>
+        <v>234243000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>566661000</v>
+        <v>235652000</v>
       </c>
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="n"/>
@@ -2994,23 +3482,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Other Operating Expenses</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>23000</v>
+        <v>654292000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>98000</v>
+        <v>657776000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3297000</v>
+        <v>642004000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>195000</v>
+        <v>597379000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>112000</v>
+        <v>566661000</v>
       </c>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n"/>
@@ -3018,23 +3506,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>499511000</v>
+        <v>23000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>493458000</v>
+        <v>98000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>497002000</v>
+        <v>3297000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>461167000</v>
+        <v>195000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>443009000</v>
+        <v>112000</v>
       </c>
       <c r="G45" s="3" t="n"/>
       <c r="H45" s="3" t="n"/>
@@ -3042,7 +3530,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization In Income Statement</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -3066,23 +3554,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>154758000</v>
+        <v>499511000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>164220000</v>
+        <v>493458000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>141705000</v>
+        <v>497002000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>136017000</v>
+        <v>461167000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>123540000</v>
+        <v>443009000</v>
       </c>
       <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
@@ -3090,7 +3578,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
@@ -3114,7 +3602,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>General And Administrative Expense</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -3138,23 +3626,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Other Gand A</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>936910000</v>
+        <v>154758000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>885036000</v>
+        <v>164220000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>866984000</v>
+        <v>141705000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>831622000</v>
+        <v>136017000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>802313000</v>
+        <v>123540000</v>
       </c>
       <c r="G50" s="3" t="n"/>
       <c r="H50" s="3" t="n"/>
@@ -3162,23 +3650,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>698263000</v>
+        <v>936910000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>749635000</v>
+        <v>885036000</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>710250000</v>
+        <v>866984000</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>661528000</v>
+        <v>831622000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>605324000</v>
+        <v>802313000</v>
       </c>
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="3" t="n"/>
@@ -3186,23 +3674,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1635173000</v>
+        <v>698263000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1634671000</v>
+        <v>749635000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1577234000</v>
+        <v>710250000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1493150000</v>
+        <v>661528000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1407637000</v>
+        <v>605324000</v>
       </c>
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="3" t="n"/>
@@ -3210,7 +3698,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -3230,13 +3718,37 @@
       </c>
       <c r="G53" s="3" t="n"/>
       <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1635173000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1634671000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1577234000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1493150000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1407637000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4640,7 +5152,1619 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Preferred Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>348924000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>343557430</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>343041161</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>340372076</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>336743461</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>348924000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>343557430</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>343041161</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>340372076</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>336743461</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>15570002000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>14950488000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>14925731000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>14898022000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>14694394000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>19215142000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>19655352000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>19510501000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>19750233000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18297851000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>11319406000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>10347322000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>10789692000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>10375006000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>9264754000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>40633696000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>40596108000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>40518774000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>40634985000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>37580187000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>436114000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>476860000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>682853000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1746955000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1056450000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>12051096000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>11079012000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11521382000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>11106696000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>9996444000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1218509000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1253217000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1285067000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1298085000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1281572000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>22637063000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>22193973000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>22293340000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>22182837000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>20563908000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>40657425000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>40428708000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>40098422000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>40798976000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>37214946000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>25397014000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>24845974000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>24989222000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>24861846000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>23178156000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2028261000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1920311000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1964192000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1947319000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1882558000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>23368753000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>22925663000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>23025030000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>22914527000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>21295598000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-7459561000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-7159920000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-6892392000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-6541363000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-7531091000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-7459561000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-7159920000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-6892392000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-6541363000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-7531091000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>30093165000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>29350487000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>29182332000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>28720826000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>28091661000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>735149000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>735096000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>735090000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>735064000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>735028000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>3459000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>3406000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>3374000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>3338000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>731690000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>23462959000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>24564494000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>23739412000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>23853149000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>21902406000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>19601136000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>19880986000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>19509833000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20319839000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>18310214000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>559768000</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>539802000</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>423797000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1093955000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1124724000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1151374000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1137305000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1109294000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1093955000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1124724000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1151374000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1137305000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1109294000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>18507181000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>18756262000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>18358459000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>19182534000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>17200920000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1218509000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1253217000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1285067000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1298085000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1281572000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>17288672000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>17503045000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>17073392000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>17884449000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>15919348000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>3861823000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>4683508000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>4229579000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3533310000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>3592192000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n">
+        <v>182000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>283000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1089000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>7882000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>733974000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>754920000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>699528000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>653640000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>559768000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>733974000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>754920000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>699528000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>653640000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>559768000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>707961000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>899090000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1152042000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>567699000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1096931000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>707961000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>899090000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1152042000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>567699000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1096931000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>707961000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>899090000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1152042000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>567699000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1096931000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2419888000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3029316000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2377726000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2310882000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1927611000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2419888000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3029316000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>2377726000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2310882000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1927611000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>428337000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2419888000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2600979000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2377726000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2310882000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1927611000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>48859973000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>49410468000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>48728634000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>48714995000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>45080562000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>44235075000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>44250100000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>43591198000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>43434730000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>40431920000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>650913000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>655377000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>500262000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>493325000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>488921000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>765198000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>750907000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>710624000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>681375000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>641290000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>3536757000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3427903000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>3690749000</v>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
+        <v>2702847000</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2639800000</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>3536757000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3427903000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>3690749000</v>
+      </c>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>2702847000</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2639800000</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Investmentsin Joint Venturesat Cost</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>2702847000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Investment Properties</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>26859470000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>26433617000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>26018517000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>29271542000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>24133784000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>11317657000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>11846651000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>11503648000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>11807831000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>11299154000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1726407000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2134698000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1855894000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2171318000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2124989000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>9591250000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>9711953000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>9647754000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>9636513000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>9174165000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1105080000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1135645000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1167398000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1180657000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1165924000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1105080000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1135645000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1167398000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1180657000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1165924000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1105080000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1135645000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1167398000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1180657000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1165924000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>4297937000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5160368000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4912432000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5280265000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>4648642000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>441064000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>349826000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>116624000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>139993000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>953236000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1430242000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1358895000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1496105000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1586146000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1373521000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>276148000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>187966000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>210871000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>194865000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>243900000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>95813000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>109816000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>194486000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>208792000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>166886000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1058281000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1061113000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1090748000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1182489000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>962735000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-79224000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>-86351000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>-85274000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-80832000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-62803000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1137505000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1147464000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1176022000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1263321000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1025538000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>2426631000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>3451647000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>3299703000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>3554126000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2321885000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2426631000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>3451647000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>3299703000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3554126000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2321885000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5700,7 +7824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6856,7 +8980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6884,12 +9008,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Capital Expenditure' not found in statements — left blank</t>
         </is>
       </c>
     </row>
